--- a/outputs/history-events-20261022/Danh_sach_su_kien_lich_su_da_bo_sung.xlsx
+++ b/outputs/history-events-20261022/Danh_sach_su_kien_lich_su_da_bo_sung.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="25605" windowHeight="11985"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách sự kiện Thế giới" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="189">
   <si>
     <t>STT</t>
   </si>
@@ -350,70 +350,43 @@
     <t>Phát minh ra máy in chữ thập (Johannes Gutenberg)</t>
   </si>
   <si>
-    <t>1440</t>
+    <t>Đại hiến chương Magna Carta được ký kết</t>
+  </si>
+  <si>
+    <t>Dịch hạch Cái chết Đen tấn công châu Âu</t>
+  </si>
+  <si>
+    <t>Thomas Edison phát minh ra bóng đèn sợi đốt thương mại</t>
+  </si>
+  <si>
+    <t>Anh em nhà Wright thực hiện chuyến bay đầu tiên</t>
+  </si>
+  <si>
+    <t>Alexander Fleming khám phá ra penicillin</t>
+  </si>
+  <si>
+    <t>Máy tính điện tử ENIAC ra đời</t>
+  </si>
+  <si>
+    <t>Tim Berners-Lee phát minh ra World Wide Web</t>
+  </si>
+  <si>
+    <t>Tàu vũ trụ Voyager 1 được phóng lên</t>
+  </si>
+  <si>
+    <t>Khánh thành tháp Eiffel tại Paris</t>
+  </si>
+  <si>
+    <t>Khánh thành tượng Nữ thần Tự do tại Mỹ</t>
+  </si>
+  <si>
+    <t>Cuộc khủng hoảng tên lửa Cuba</t>
+  </si>
+  <si>
+    <t>1962</t>
   </si>
   <si>
     <t>Chưa có ảnh</t>
-  </si>
-  <si>
-    <t>Đại hiến chương Magna Carta được ký kết</t>
-  </si>
-  <si>
-    <t>Dịch hạch Cái chết Đen tấn công châu Âu</t>
-  </si>
-  <si>
-    <t>1347</t>
-  </si>
-  <si>
-    <t>Vụ ném bom nguyên tử xuống Hiroshima và Nagasaki</t>
-  </si>
-  <si>
-    <t>Thomas Edison phát minh ra bóng đèn sợi đốt thương mại</t>
-  </si>
-  <si>
-    <t>1879</t>
-  </si>
-  <si>
-    <t>Anh em nhà Wright thực hiện chuyến bay đầu tiên</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>Alexander Fleming khám phá ra penicillin</t>
-  </si>
-  <si>
-    <t>1928</t>
-  </si>
-  <si>
-    <t>Máy tính điện tử ENIAC ra đời</t>
-  </si>
-  <si>
-    <t>Tim Berners-Lee phát minh ra World Wide Web</t>
-  </si>
-  <si>
-    <t>Tàu vũ trụ Voyager 1 được phóng lên</t>
-  </si>
-  <si>
-    <t>1977</t>
-  </si>
-  <si>
-    <t>Khánh thành tháp Eiffel tại Paris</t>
-  </si>
-  <si>
-    <t>1889</t>
-  </si>
-  <si>
-    <t>Khánh thành tượng Nữ thần Tự do tại Mỹ</t>
-  </si>
-  <si>
-    <t>1886</t>
-  </si>
-  <si>
-    <t>Cuộc khủng hoảng tên lửa Cuba</t>
-  </si>
-  <si>
-    <t>1962</t>
   </si>
   <si>
     <t>Thảm họa hạt nhân Chernobyl</t>
@@ -1808,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2555,11 +2528,11 @@
       <c r="B53" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>107</v>
+      <c r="C53" s="2">
+        <v>1440</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2567,13 +2540,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1215</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2581,13 +2554,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1347</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2595,13 +2568,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1879</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2609,13 +2582,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1903</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2623,13 +2596,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1928</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2637,13 +2610,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1945</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2651,13 +2624,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2665,13 +2638,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1977</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2679,13 +2652,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1889</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2693,13 +2666,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1886</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2707,13 +2680,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2721,13 +2694,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2735,13 +2708,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2749,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2763,13 +2736,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2777,13 +2750,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2791,13 +2764,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2805,13 +2778,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2819,13 +2792,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2833,13 +2806,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2847,13 +2820,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2861,13 +2834,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2875,13 +2848,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2889,13 +2862,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2903,13 +2876,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2917,13 +2890,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2931,13 +2904,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2945,13 +2918,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2959,13 +2932,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2973,13 +2946,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2987,13 +2960,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3001,13 +2974,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3015,13 +2988,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3029,13 +3002,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3043,13 +3016,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3057,13 +3030,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3071,13 +3044,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>176</v>
+        <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3085,13 +3058,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3099,13 +3072,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3113,13 +3086,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3127,13 +3100,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3141,13 +3114,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3155,13 +3128,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3169,13 +3142,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3183,13 +3156,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3197,13 +3170,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>192</v>
+        <v>57</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3211,13 +3184,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>57</v>
+        <v>186</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3225,32 +3198,18 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="2">
-        <v>101</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D102">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D55 D56:D101">
       <formula1>"Đã có ảnh,Chưa có ảnh"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/history-events-20261022/Danh_sach_su_kien_lich_su_da_bo_sung.xlsx
+++ b/outputs/history-events-20261022/Danh_sach_su_kien_lich_su_da_bo_sung.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25605" windowHeight="11985"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách sự kiện Thế giới" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="176">
   <si>
     <t>STT</t>
   </si>
@@ -392,15 +392,9 @@
     <t>Thảm họa hạt nhân Chernobyl</t>
   </si>
   <si>
-    <t>1986</t>
-  </si>
-  <si>
     <t>James Watt cấp bằng sáng chế cho động cơ hơi nước cải tiến</t>
   </si>
   <si>
-    <t>1769</t>
-  </si>
-  <si>
     <t>Chiến tranh Triều Tiên bùng nổ</t>
   </si>
   <si>
@@ -434,21 +428,12 @@
     <t>Thành Cát Tư Hãn thống nhất các bộ lạc Mông Cổ</t>
   </si>
   <si>
-    <t>1206</t>
-  </si>
-  <si>
     <t>Đường sắt chở khách đầu tiên đi vào hoạt động (Anh)</t>
   </si>
   <si>
-    <t>1825</t>
-  </si>
-  <si>
     <t>Kênh đào Suez chính thức khánh thành</t>
   </si>
   <si>
-    <t>1869</t>
-  </si>
-  <si>
     <t>Hội Quốc Liên được thành lập</t>
   </si>
   <si>
@@ -473,15 +458,9 @@
     <t>Nelson Mandela trở thành Tổng thống da đen đầu tiên của Nam Phi</t>
   </si>
   <si>
-    <t>1994</t>
-  </si>
-  <si>
     <t>Mỹ bãi bỏ chế độ nô lệ (Tu chính án thứ 13)</t>
   </si>
   <si>
-    <t>1865</t>
-  </si>
-  <si>
     <t>Mahatma Gandhi dẫn đầu cuộc Tuần hành Muối</t>
   </si>
   <si>
@@ -500,27 +479,15 @@
     <t>Thảm họa hạt nhân Fukushima</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>Giải Nobel đầu tiên được trao</t>
   </si>
   <si>
-    <t>1901</t>
-  </si>
-  <si>
     <t>Kính viễn vọng không gian Hubble được phóng</t>
   </si>
   <si>
-    <t>1990</t>
-  </si>
-  <si>
     <t>Anh em nhà Lumière tổ chức buổi chiếu phim thương mại đầu tiên</t>
   </si>
   <si>
-    <t>1895</t>
-  </si>
-  <si>
     <t>Joan of Arc giải vây Orléans</t>
   </si>
   <si>
@@ -545,9 +512,6 @@
     <t>Phát hành đồng tiền chung châu Âu (Euro)</t>
   </si>
   <si>
-    <t>1999</t>
-  </si>
-  <si>
     <t>Khởi công xây dựng Vạn Lý Trường Thành (Tần Thủy Hoàng)</t>
   </si>
   <si>
@@ -576,9 +540,6 @@
   </si>
   <si>
     <t>Nữ hoàng Elizabeth II lên ngôi</t>
-  </si>
-  <si>
-    <t>1952</t>
   </si>
   <si>
     <t>Chế độ phân biệt chủng tộc Apartheid bị bãi bỏ tại Nam Phi</t>
@@ -2696,11 +2657,11 @@
       <c r="B65" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>121</v>
+      <c r="C65" s="2">
+        <v>1986</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2708,13 +2669,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1769</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2722,10 +2683,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>119</v>
@@ -2736,13 +2697,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2750,10 +2711,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>119</v>
@@ -2764,13 +2725,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2778,13 +2739,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2792,13 +2753,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1206</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2806,13 +2767,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1825</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2820,13 +2781,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1869</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2834,13 +2795,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2848,13 +2809,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2862,13 +2823,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2876,13 +2837,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2890,13 +2851,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1994</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2904,13 +2865,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1865</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2918,10 +2879,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>119</v>
@@ -2932,13 +2893,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2946,13 +2907,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1869</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2960,13 +2921,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
+      </c>
+      <c r="C84" s="2">
+        <v>2011</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2974,13 +2935,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1901</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2988,13 +2949,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1990</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3002,13 +2963,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1895</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3016,10 +2977,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>119</v>
@@ -3030,10 +2991,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>119</v>
@@ -3044,7 +3005,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
@@ -3058,10 +3019,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>119</v>
@@ -3072,13 +3033,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>172</v>
+        <v>160</v>
+      </c>
+      <c r="C92" s="2">
+        <v>1999</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3086,10 +3047,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>119</v>
@@ -3100,10 +3061,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>119</v>
@@ -3114,10 +3075,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>119</v>
@@ -3128,10 +3089,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>119</v>
@@ -3142,7 +3103,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>103</v>
@@ -3156,13 +3117,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
+      </c>
+      <c r="C98" s="2">
+        <v>1952</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3170,7 +3131,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>57</v>
@@ -3184,10 +3145,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>119</v>
@@ -3198,10 +3159,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>119</v>
@@ -3209,7 +3170,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D55 D56:D101">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D101">
       <formula1>"Đã có ảnh,Chưa có ảnh"</formula1>
     </dataValidation>
   </dataValidations>
